--- a/samples/예시데이터_가스기술사학습.xlsx
+++ b/samples/예시데이터_가스기술사학습.xlsx
@@ -2095,55 +2095,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>카드번호</v>
       </c>
       <c r="B1" t="str">
-        <v>기술명</v>
+        <v>제목</v>
       </c>
       <c r="C1" t="str">
-        <v>연도</v>
+        <v>목차</v>
       </c>
       <c r="D1" t="str">
-        <v>기술 분야</v>
+        <v>내용</v>
       </c>
       <c r="E1" t="str">
-        <v>관련 영역번호</v>
+        <v>작성 일시</v>
       </c>
       <c r="F1" t="str">
-        <v>기술 정의</v>
-      </c>
-      <c r="G1" t="str">
-        <v>기존 기술의 문제점</v>
-      </c>
-      <c r="H1" t="str">
-        <v>핵심 기술</v>
-      </c>
-      <c r="I1" t="str">
-        <v>적용 분야</v>
-      </c>
-      <c r="J1" t="str">
-        <v>향후 발전방향</v>
-      </c>
-      <c r="K1" t="str">
-        <v>출처_문서명</v>
-      </c>
-      <c r="L1" t="str">
-        <v>출처_발행기관</v>
-      </c>
-      <c r="M1" t="str">
-        <v>출처_URL</v>
-      </c>
-      <c r="N1" t="str">
-        <v>출처 확인(Y)</v>
-      </c>
-      <c r="O1" t="str">
-        <v>작성 일시</v>
-      </c>
-      <c r="P1" t="str">
         <v>수정 일시</v>
       </c>
     </row>
@@ -2152,54 +2122,24 @@
         <v>TEC-001</v>
       </c>
       <c r="B2" t="str">
-        <v>(예시 카드) 양식 확인용 — 실제 기술 정보가 아닙니다</v>
+        <v>(예시 카드) 양식 확인용 — 실제 공부 내용이 아닙니다</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>수소안전</v>
       </c>
       <c r="D2" t="str">
-        <v>기타</v>
+        <v>공부한 내용을 자유롭게 적는 칸입니다. 저장하면 고른 목차(여기서는 「수소안전」) 아래에 쌓입니다.</v>
       </c>
       <c r="E2" t="str">
-        <v>8</v>
+        <v>2026-09-27 10:00</v>
       </c>
       <c r="F2" t="str">
-        <v>기술 정의를 적는 칸입니다.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>기존 기술의 문제점을 적는 칸입니다.</v>
-      </c>
-      <c r="H2" t="str">
-        <v>핵심 기술을 적는 칸입니다.</v>
-      </c>
-      <c r="I2" t="str">
-        <v>적용 분야를 적는 칸입니다.</v>
-      </c>
-      <c r="J2" t="str">
-        <v>향후 발전방향을 적는 칸입니다.</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v>2026-09-27 10:00</v>
-      </c>
-      <c r="P2" t="str">
         <v>2026-09-27 10:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>